--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>64614.03</v>
+        <v>64961.98</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>39361.41</v>
+        <v>39801.61</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17165.73</v>
+        <v>17357.71</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>56220.72</v>
+        <v>56849.47</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>35281.6</v>
+        <v>35415.26</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>23562.73</v>
+        <v>23503.24</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>21054.26</v>
+        <v>21001.1</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>73156.32000000001</v>
+        <v>73851.35000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>65299.55</v>
+        <v>65919.94</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>47069.77</v>
+        <v>47516.97</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>39953.46</v>
+        <v>40333.05</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>30293.61</v>
+        <v>30519.29</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12940.3</v>
+        <v>13036.7</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>25640.39</v>
+        <v>25831.41</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>14650.23</v>
+        <v>14759.37</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>27523.12</v>
+        <v>27728.17</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>39351.07</v>
+        <v>39644.24</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>29685.11</v>
+        <v>29906.26</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>38805.41</v>
+        <v>38418.41</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>74376.7</v>
+        <v>74050.67999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>33143.32</v>
+        <v>32998.04</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>34079.44</v>
+        <v>33930.06</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41398.65</v>
+        <v>41217.18</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>70563.2</v>
+        <v>69795.59</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>56137.34</v>
+        <v>55526.66</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>25640.39</v>
+        <v>25361.47</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>41735.74</v>
+        <v>41281.73</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>78587.59</v>
+        <v>78409.21000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>57276.38</v>
+        <v>57146.37</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>36985.96</v>
+        <v>36894.63</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>33856.08</v>
+        <v>33772.48</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27015.92</v>
+        <v>27148.63</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>38823.26</v>
+        <v>39013.97</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>14650.23</v>
+        <v>14698.83</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>39361.41</v>
+        <v>39491.98</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13838.47</v>
+        <v>13882.51</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>39581.29</v>
+        <v>39707.27</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14338.52</v>
+        <v>14384.16</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>13548.53</v>
+        <v>13591.65</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>35934.53</v>
+        <v>36048.9</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>17885.04</v>
+        <v>17941.96</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>38791.81</v>
+        <v>38915.28</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>56081.08</v>
+        <v>56259.57</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>54587.71</v>
+        <v>54877.98</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>38791.81</v>
+        <v>38998.09</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>25402.58</v>
+        <v>25537.65</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>42037.07</v>
+        <v>42260.6</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41398.65</v>
+        <v>41618.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
@@ -623,7 +623,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1586,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2163,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2228,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2293,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2484,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2549,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2614,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2679,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2744,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2870,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2935,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3000,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3065,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3130,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3195,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3260,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3325,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3390,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3455,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3520,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -818,7 +822,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2037,7 +2045,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
@@ -2403,7 +2403,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
